--- a/data/trans_dic/IP31KM10_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM10_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,54; 50,37</t>
+          <t>45,47; 62,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,65; 60,94</t>
+          <t>34,12; 50,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,27; 54,19</t>
+          <t>43,32; 54,63</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,65; 57,82</t>
+          <t>47,8; 67,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,86; 65,21</t>
+          <t>42,24; 60,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,99; 59,93</t>
+          <t>48,4; 60,95</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>50,41%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>56,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,09; 63,75</t>
+          <t>48,95; 70,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,25; 68,78</t>
+          <t>37,05; 63,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,83; 62,81</t>
+          <t>48,64; 66,15</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 73,9</t>
+          <t>47,01; 61,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,01; 60,07</t>
+          <t>46,67; 59,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49,82; 63,57</t>
+          <t>48,76; 58,07</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,42; 59,92</t>
+          <t>56,35; 72,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>54,56; 72,57</t>
+          <t>44,39; 59,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,56; 64,75</t>
+          <t>53,04; 64,56</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,1; 68,04</t>
+          <t>55,42; 76,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>52,2; 73,54</t>
+          <t>46,99; 69,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>53,44; 68,26</t>
+          <t>55,37; 70,39</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48,4; 59,13</t>
+          <t>54,38; 61,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53,02; 60,66</t>
+          <t>47,75; 54,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51,93; 58,61</t>
+          <t>52,56; 57,55</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42122</t>
+          <t>65458</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70700</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112823</t>
+          <t>108034</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34113; 51232</t>
+          <t>55119; 75301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57652; 82373</t>
+          <t>34238; 50981</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97759; 128360</t>
+          <t>95982; 121027</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>46448</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>53022</t>
+          <t>48572</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99470</t>
+          <t>100462</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37961; 53995</t>
+          <t>42967; 60279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43915; 61105</t>
+          <t>40299; 57781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87925; 112134</t>
+          <t>89684; 112940</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>38</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25249</t>
+          <t>33754</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60872</t>
+          <t>60434</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19579; 31933</t>
+          <t>27338; 39497</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28207; 42876</t>
+          <t>19269; 33038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51528; 70613</t>
+          <t>52459; 71347</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>125678</t>
+          <t>105775</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>112467</t>
+          <t>93152</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238145</t>
+          <t>198928</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>106255; 159278</t>
+          <t>92757; 121397</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97834; 127748</t>
+          <t>82433; 104257</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>213323; 272216</t>
+          <t>182324; 217169</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59525</t>
+          <t>93060</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>60301</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160254</t>
+          <t>153361</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>50156; 69209</t>
+          <t>82036; 105426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87009; 115715</t>
+          <t>51253; 68857</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144528; 178051</t>
+          <t>138466; 168528</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>44254</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83985</t>
+          <t>85881</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>32447; 46873</t>
+          <t>36504; 50513</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36035; 50764</t>
+          <t>33061; 48554</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>73707; 94142</t>
+          <t>75418; 95883</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>454</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>338751</t>
+          <t>394096</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>416796</t>
+          <t>313003</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>755548</t>
+          <t>707100</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>312245; 381492</t>
+          <t>367419; 415659</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>388301; 444266</t>
+          <t>291406; 333591</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>715309; 807334</t>
+          <t>675845; 740067</t>
         </is>
       </c>
     </row>
